--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Idris arrive en classe avec maman. Maman dit au revoir. Idris s'assoit sur le tapis. La maîtresse pose une question. Idris a une idée. Il lève la main. Il faut attendre. Un camarade parle d'abord. Idris attend encore. Puis la maîtresse dit : Idris, c'est ton tour. Idris parle. Il dit : le hérisson a des piquants. La maîtresse sourit. Plus tard, c'est le goûter. Idris a envie de raconter son goûter. Il lève la main. Il faut attendre. Une camarade parle. Idris attend. Puis la maîtresse dit : Idris. Idris parle. Il dit : j'ai une pomme. Sur le tapis, puis au goûter, c'est pareil. On lève la main. Il faut attendre. Puis parler. Le soir, maman demande. Idris dit : j'ai levé la main. J'ai su attendre. Puis j'ai parlé. Maman dit merci. Idris range son cartable.</t>
+          <t>Idris arrive en classe avec maman. Maman dit au revoir. Idris s'assoit sur le tapis. La maîtresse pose une question. Idris a une idée. Il lève la main. Il faut attendre. Un camarade parle d'abord. Idris attend encore. Puis Idris, c'est ton tour. Idris parle. Le hérisson a des piquants. La maîtresse sourit. Plus tard, c'est le goûter. Idris a envie de raconter son goûter. Il lève la main. Il faut attendre. Une camarade parle. Idris attend. Puis Idris. Idris parle. J'ai une pomme. Sur le tapis, puis au goûter, c'est pareil. On lève la main. Il faut attendre. Puis parler. Le soir, maman demande. J'ai levé la main. J'ai su attendre. Puis j'ai parlé. Maman dit merci. Idris range son cartable.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,21 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Idris arrive en classe avec maman. Maman dit au revoir. Idris s'assoit sur le tapis. La maîtresse pose une question. Idris a une idée. Il lève la main. Il faut attendre. Un camarade parle d'abord. Idris attend encore. Puis
+maitresse|Idris, c'est ton tour.
+narrateur|Idris parle.
+narrateur|Le hérisson a des piquants.
+narrateur|La maîtresse sourit. Plus tard, c'est le goûter. Idris a envie de raconter son goûter. Il lève la main. Il faut attendre. Une camarade parle. Idris attend. Puis
+maitresse|Idris.
+narrateur|Idris parle.
+narrateur|J'ai une pomme. Sur le tapis, puis au goûter, c'est pareil. On lève la main. Il faut attendre.
+narrateur|Puis parler. Le soir, maman demande.
+enfant-m|J'ai levé la main. J'ai su attendre.
+narrateur|Puis j'ai parlé. Maman dit merci. Idris range son cartable.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Idris veut parler. Que fait-il d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Idris a levé la main. Il a attendu. Puis il a parlé. C'était son tour.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Idris met son manteau. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1320,6 +1325,7 @@
 narrateur|Puis j'ai parlé. Maman dit merci. Idris range son cartable.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Idris veut parler. Que fait-il d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Idris a levé la main. Il a attendu. Puis il a parlé. C'était son tour.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Idris met son manteau. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Idris attend son tour de parole</t>
+          <t>Le hérisson de Nina</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COL.ECO.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina parle du hérisson sur le tapis. Au goûter, elle lève encore la main pour sa pomme. Elle attend. Puis elle parle.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Idris arrive en classe avec maman. Maman dit au revoir. Idris s'assoit sur le tapis. La maîtresse pose une question. Idris a une idée. Il lève la main. Il faut attendre. Un camarade parle d'abord. Idris attend encore. Puis Idris, c'est ton tour. Idris parle. Le hérisson a des piquants. La maîtresse sourit. Plus tard, c'est le goûter. Idris a envie de raconter son goûter. Il lève la main. Il faut attendre. Une camarade parle. Idris attend. Puis Idris. Idris parle. J'ai une pomme. Sur le tapis, puis au goûter, c'est pareil. On lève la main. Il faut attendre. Puis parler. Le soir, maman demande. J'ai levé la main. J'ai su attendre. Puis j'ai parlé. Maman dit merci. Idris range son cartable.</t>
+          <t>Près de la haie de l'école, l'herbe est encore mouillée. Une affiche un peu de travers montre un hérisson. Les piquants sont dessinés au crayon brun. Maman tient le cartable de Nina. Le cartable est un peu humide, dehors. Tu vas t'asseoir sur le tapis ? Oui, maman. Papa a mis une pomme dans la boîte. La pomme est pour le goûter. Tu attends ton tour, d'accord ? D'accord, papa. En ce moment, Nina entre dans la classe avec maman. Au revoir, Nina. Bonne journée. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, encore. La maîtresse montre l'affiche du hérisson. Qui veut parler du hérisson ? Nina a une idée. Elle lève la main. Il faut attendre. Quelqu'un parle d'abord. Nina attend encore. Sa main reste en l'air. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,20 +1329,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Idris arrive en classe avec maman. Maman dit au revoir. Idris s'assoit sur le tapis. La maîtresse pose une question. Idris a une idée. Il lève la main. Il faut attendre. Un camarade parle d'abord. Idris attend encore. Puis
-maitresse|Idris, c'est ton tour.
-narrateur|Idris parle.
-narrateur|Le hérisson a des piquants.
-narrateur|La maîtresse sourit. Plus tard, c'est le goûter. Idris a envie de raconter son goûter. Il lève la main. Il faut attendre. Une camarade parle. Idris attend. Puis
-maitresse|Idris.
-narrateur|Idris parle.
-narrateur|J'ai une pomme. Sur le tapis, puis au goûter, c'est pareil. On lève la main. Il faut attendre.
-narrateur|Puis parler. Le soir, maman demande.
-enfant-m|J'ai levé la main. J'ai su attendre.
-narrateur|Puis j'ai parlé. Maman dit merci. Idris range son cartable.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Près de la haie de l'école, l'herbe est encore mouillée.
+narrateur|Une affiche un peu de travers montre un hérisson.
+narrateur|Les piquants sont dessinés au crayon brun.
+narrateur|Maman tient le cartable de Nina.
+maman|Le cartable est un peu humide, dehors.
+maman|Tu vas t'asseoir sur le tapis ?
+enfant-f|Oui, maman.
+narrateur|Papa a mis une pomme dans la boîte.
+papa|La pomme est pour le goûter.
+papa|Tu attends ton tour, d'accord ?
+enfant-f|D'accord, papa.
+narrateur|En ce moment, Nina entre dans la classe avec maman.
+maman|Au revoir, Nina.
+maman|Bonne journée.
+enfant-f|Au revoir, maman.
+narrateur|Nina s'assoit sur le tapis.
+narrateur|Le tapis est un peu froid, encore.
+narrateur|La maîtresse montre l'affiche du hérisson.
+maitresse|Qui veut parler du hérisson ?
+narrateur|Nina a une idée.
+narrateur|Elle lève la main.
+narrateur|Il faut attendre.
+narrateur|Quelqu'un parle d'abord.
+narrateur|Nina attend encore.
+narrateur|Sa main reste en l'air.
+enfant-f|J'attends. Puis je parle.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>haie,porte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,7 +1386,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Idris veut parler. Que fait-il d'abord ?</t>
+          <t>Nina veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1542,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Idris veut parler. Que fait-il d'abord ?</t>
+          <t>narrateur|Nina veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1570,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Idris a levé la main. Il a attendu. Puis il a parlé. C'était son tour.</t>
+          <t>Nina, c'est ton tour. Nina parle. Le hérisson a des piquants. Merci, Nina. Tu as attendu. Puis tu as parlé. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme. Nina a envie de raconter son goûter. Elle lève la main. Il faut attendre. Quelqu'un parle. Nina attend. Nina. J'ai une pomme. Merci. Sur le tapis, puis au goûter, c'est pareil. On lève la main. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,10 +1714,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Idris a levé la main. Il a attendu. Puis il a parlé. C'était son tour.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>maitresse|Nina, c'est ton tour.
+narrateur|Nina parle.
+enfant-f|Le hérisson a des piquants.
+maitresse|Merci, Nina.
+maitresse|Tu as attendu. Puis tu as parlé.
+narrateur|Plus tard, c'est le goûter.
+narrateur|Les boîtes s'ouvrent. Ça sent la pomme.
+narrateur|Nina a envie de raconter son goûter.
+narrateur|Elle lève la main.
+narrateur|Il faut attendre.
+narrateur|Quelqu'un parle.
+narrateur|Nina attend.
+maitresse|Nina.
+enfant-f|J'ai une pomme.
+maitresse|Merci. Sur le tapis, puis au goûter, c'est pareil.
+maitresse|On lève la main. On attend. Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>boite,pomme</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,7 +1761,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Idris met son manteau. Maman l'attend à la porte.</t>
+          <t>Le soir, maman demande près de la porte. Alors, Nina ? J'ai levé la main. J'ai su attendre. Puis j'ai parlé. Bravo, Nina. Tu as fait du bon travail. Tu as attendu au goûter aussi ? Oui, maman. Nina met son manteau. Maman l'attend à la porte. Bravo. Tu as attendu. Puis tu as parlé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,10 +1897,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Idris met son manteau. Maman l'attend à la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le soir, maman demande près de la porte.
+maman|Alors, Nina ?
+enfant-f|J'ai levé la main.
+enfant-f|J'ai su attendre.
+enfant-f|Puis j'ai parlé.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|Tu as attendu au goûter aussi ?
+enfant-f|Oui, maman.
+narrateur|Nina met son manteau.
+narrateur|Maman l'attend à la porte.
+maman|Bravo. Tu as attendu. Puis tu as parlé.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>porte,manteau</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,7 +1940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Nina. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2080,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis j'ai parlé.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Près de la haie de l'école, l'herbe est encore mouillée. Une affiche un peu de travers montre un hérisson. Les piquants sont dessinés au crayon brun. Maman tient le cartable de Nina. Le cartable est un peu humide, dehors. Tu vas t'asseoir sur le tapis ? Oui, maman. Papa a mis une pomme dans la boîte. La pomme est pour le goûter. Tu attends ton tour, d'accord ? D'accord, papa. En ce moment, Nina entre dans la classe avec maman. Au revoir, Nina. Bonne journée. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, encore. La maîtresse montre l'affiche du hérisson. Qui veut parler du hérisson ? Nina a une idée. Elle lève la main. Il faut attendre. Quelqu'un parle d'abord. Nina attend encore. Sa main reste en l'air. J'attends. Puis je parle.</t>
+          <t>Près de la haie de l'école, l'herbe est encore mouillée. Une affiche un peu de travers montre un hérisson. Les piquants sont dessinés au crayon brun. Maman tient le cartable de Nina. Le cartable est un peu humide, dehors. Tu vas t'asseoir sur le tapis ? Oui, maman. Papa a mis une pomme dans la boîte. La pomme est pour le goûter. Tu attends ton tour, d'accord ? D'accord, papa. En ce moment, Nina entre dans la classe avec maman. Au revoir, Nina. Bonne journée. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, encore. Une goutte de la haie brille encore sur la chaussure. La maîtresse montre l'affiche du hérisson. Les piquants sont un peu de travers. On écoute d'abord l'affiche. Qui veut parler du hérisson ? Nina a une idée. Elle lève la main. Il faut attendre. Quelqu'un parle d'abord. Nina attend encore. Sa main reste en l'air. Elle pense à la pomme dans la boîte. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1346,7 +1346,10 @@
 enfant-f|Au revoir, maman.
 narrateur|Nina s'assoit sur le tapis.
 narrateur|Le tapis est un peu froid, encore.
+narrateur|Une goutte de la haie brille encore sur la chaussure.
 narrateur|La maîtresse montre l'affiche du hérisson.
+narrateur|Les piquants sont un peu de travers.
+maitresse|On écoute d'abord l'affiche.
 maitresse|Qui veut parler du hérisson ?
 narrateur|Nina a une idée.
 narrateur|Elle lève la main.
@@ -1354,7 +1357,9 @@
 narrateur|Quelqu'un parle d'abord.
 narrateur|Nina attend encore.
 narrateur|Sa main reste en l'air.
-enfant-f|J'attends. Puis je parle.</t>
+narrateur|Elle pense à la pomme dans la boîte.
+enfant-f|J'attends.
+enfant-f|Puis je parle.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1542,7 +1547,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nina veut parler. Que fait-elle d'abord ?</t>
+          <t>narrateur|Nina veut parler.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1570,7 +1576,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina, c'est ton tour. Nina parle. Le hérisson a des piquants. Merci, Nina. Tu as attendu. Puis tu as parlé. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme. Nina a envie de raconter son goûter. Elle lève la main. Il faut attendre. Quelqu'un parle. Nina attend. Nina. J'ai une pomme. Merci. Sur le tapis, puis au goûter, c'est pareil. On lève la main. On attend. Puis on parle.</t>
+          <t>Nina, c'est ton tour. Nina parle. Le hérisson a des piquants. Merci, Nina. Tu as attendu. Puis tu as parlé. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme. La pomme de Nina est verte, un peu brillante. Nina a envie de raconter son goûter. Elle lève la main. Il faut attendre. Quelqu'un parle. Nina attend. Elle pose la pomme devant elle. Nina. J'ai une pomme. Merci. Sur le tapis, puis au goûter, c'est pareil. On lève la main. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1718,18 +1724,25 @@
 narrateur|Nina parle.
 enfant-f|Le hérisson a des piquants.
 maitresse|Merci, Nina.
-maitresse|Tu as attendu. Puis tu as parlé.
+maitresse|Tu as attendu.
+maitresse|Puis tu as parlé.
 narrateur|Plus tard, c'est le goûter.
-narrateur|Les boîtes s'ouvrent. Ça sent la pomme.
+narrateur|Les boîtes s'ouvrent.
+narrateur|Ça sent la pomme.
+narrateur|La pomme de Nina est verte, un peu brillante.
 narrateur|Nina a envie de raconter son goûter.
 narrateur|Elle lève la main.
 narrateur|Il faut attendre.
 narrateur|Quelqu'un parle.
 narrateur|Nina attend.
+narrateur|Elle pose la pomme devant elle.
 maitresse|Nina.
 enfant-f|J'ai une pomme.
-maitresse|Merci. Sur le tapis, puis au goûter, c'est pareil.
-maitresse|On lève la main. On attend. Puis on parle.</t>
+maitresse|Merci.
+maitresse|Sur le tapis, puis au goûter, c'est pareil.
+maitresse|On lève la main.
+maitresse|On attend.
+maitresse|Puis on parle.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1908,7 +1921,9 @@
 enfant-f|Oui, maman.
 narrateur|Nina met son manteau.
 narrateur|Maman l'attend à la porte.
-maman|Bravo. Tu as attendu. Puis tu as parlé.</t>
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2081,7 +2096,8 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>enfant-f|J'ai levé la main.
-enfant-f|J'ai attendu. Puis j'ai parlé.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
 maman|Bravo, Nina.
 papa|Tu as fait du bon travail.
 narrateur|L'histoire est finie.</t>
@@ -2106,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2165,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le hérisson de Nina</t>
+          <t>La pomme de pin de Nina</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina parle du hérisson sur le tapis. Au goûter, elle lève encore la main pour sa pomme. Elle attend. Puis elle parle.</t>
+          <t>Une pomme de pin roule dans la poche. Nina veut la montrer près du hérisson. Elle attend, elle parle, puis au goûter elle attend encore pour sa pomme verte.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Près de la haie de l'école, l'herbe est encore mouillée. Une affiche un peu de travers montre un hérisson. Les piquants sont dessinés au crayon brun. Maman tient le cartable de Nina. Le cartable est un peu humide, dehors. Tu vas t'asseoir sur le tapis ? Oui, maman. Papa a mis une pomme dans la boîte. La pomme est pour le goûter. Tu attends ton tour, d'accord ? D'accord, papa. En ce moment, Nina entre dans la classe avec maman. Au revoir, Nina. Bonne journée. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, encore. Une goutte de la haie brille encore sur la chaussure. La maîtresse montre l'affiche du hérisson. Les piquants sont un peu de travers. On écoute d'abord l'affiche. Qui veut parler du hérisson ? Nina a une idée. Elle lève la main. Il faut attendre. Quelqu'un parle d'abord. Nina attend encore. Sa main reste en l'air. Elle pense à la pomme dans la boîte. J'attends. Puis je parle.</t>
+          <t>Une pomme de pin roule dans la poche. Elle chatouille les doigts, tout sec. Un filet d'escargot brille sur le mur. L'air sent la mousse froide. Maman tient le cartable de Nina. Le cartable est un peu humide, dehors. Tu vas t'asseoir sur le tapis ? Oui, maman. Je veux montrer la pomme de pin. Près du hérisson. La pomme verte est pour le goûter. Tu attends ton tour, d'accord ? D'accord, papa. En ce moment, Nina entre dans la classe. Au revoir, Nina. Bonne journée. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, encore. La pomme de pin reste dans la poche. La maîtresse montre une affiche. C'est un hérisson. Les piquants sont dessinés au crayon brun. On écoute d'abord l'affiche. Qui veut parler du hérisson ? Nina a une idée. Les piquants ressemblent à la pomme de pin. Elle a envie de le dire. Je veux parler des piquants.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1329,42 +1329,40 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Près de la haie de l'école, l'herbe est encore mouillée.
-narrateur|Une affiche un peu de travers montre un hérisson.
-narrateur|Les piquants sont dessinés au crayon brun.
+          <t>narrateur|Une pomme de pin roule dans la poche.
+narrateur|Elle chatouille les doigts, tout sec.
+narrateur|Un filet d'escargot brille sur le mur.
+narrateur|L'air sent la mousse froide.
 narrateur|Maman tient le cartable de Nina.
 maman|Le cartable est un peu humide, dehors.
 maman|Tu vas t'asseoir sur le tapis ?
 enfant-f|Oui, maman.
-narrateur|Papa a mis une pomme dans la boîte.
-papa|La pomme est pour le goûter.
+enfant-f|Je veux montrer la pomme de pin.
+enfant-f|Près du hérisson.
+papa|La pomme verte est pour le goûter.
 papa|Tu attends ton tour, d'accord ?
 enfant-f|D'accord, papa.
-narrateur|En ce moment, Nina entre dans la classe avec maman.
+narrateur|En ce moment, Nina entre dans la classe.
 maman|Au revoir, Nina.
 maman|Bonne journée.
 enfant-f|Au revoir, maman.
 narrateur|Nina s'assoit sur le tapis.
 narrateur|Le tapis est un peu froid, encore.
-narrateur|Une goutte de la haie brille encore sur la chaussure.
-narrateur|La maîtresse montre l'affiche du hérisson.
-narrateur|Les piquants sont un peu de travers.
+narrateur|La pomme de pin reste dans la poche.
+narrateur|La maîtresse montre une affiche.
+narrateur|C'est un hérisson.
+narrateur|Les piquants sont dessinés au crayon brun.
 maitresse|On écoute d'abord l'affiche.
 maitresse|Qui veut parler du hérisson ?
 narrateur|Nina a une idée.
-narrateur|Elle lève la main.
-narrateur|Il faut attendre.
-narrateur|Quelqu'un parle d'abord.
-narrateur|Nina attend encore.
-narrateur|Sa main reste en l'air.
-narrateur|Elle pense à la pomme dans la boîte.
-enfant-f|J'attends.
-enfant-f|Puis je parle.</t>
+narrateur|Les piquants ressemblent à la pomme de pin.
+narrateur|Elle a envie de le dire.
+enfant-f|Je veux parler des piquants.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>haie,porte</t>
+          <t>poche,porte</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1409,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>attendre | il attend | lever la main | la main</t>
+          <t>attendre | elle attend | lever la main | la main</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1426,7 +1424,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il lève la main et il attend. Que fait Idris ?</t>
+          <t>Elle lève la main et elle attend. Que fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1551,7 +1549,6 @@
 narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1576,7 +1573,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina, c'est ton tour. Nina parle. Le hérisson a des piquants. Merci, Nina. Tu as attendu. Puis tu as parlé. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme. La pomme de Nina est verte, un peu brillante. Nina a envie de raconter son goûter. Elle lève la main. Il faut attendre. Quelqu'un parle. Nina attend. Elle pose la pomme devant elle. Nina. J'ai une pomme. Merci. Sur le tapis, puis au goûter, c'est pareil. On lève la main. On attend. Puis on parle.</t>
+          <t>Nina lève la main. Sa main reste en l'air. Il faut attendre. Elle attend. Quelqu'un parle d'abord. Nina attend encore. Nina, c'est ton tour. Nina parle. Le hérisson a des piquants. Comme ma pomme de pin. Elle la pose près de l'affiche. Les piquants et les écailles se regardent. Merci, Nina. Tu as attendu. Puis tu as parlé. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme. La pomme de Nina est verte, un peu brillante. Nina a envie de raconter son goûter. Elle lève la main. Elle attend. Quelqu'un parle. Nina. J'ai une pomme verte. Merci. Sur le tapis, puis au goûter, c'est pareil.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1644,7 +1641,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1720,9 +1717,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>maitresse|Nina, c'est ton tour.
+          <t>narrateur|Nina lève la main.
+narrateur|Sa main reste en l'air.
+narrateur|Il faut attendre.
+narrateur|Elle attend.
+narrateur|Quelqu'un parle d'abord.
+narrateur|Nina attend encore.
+maitresse|Nina, c'est ton tour.
 narrateur|Nina parle.
 enfant-f|Le hérisson a des piquants.
+enfant-f|Comme ma pomme de pin.
+narrateur|Elle la pose près de l'affiche.
+narrateur|Les piquants et les écailles se regardent.
 maitresse|Merci, Nina.
 maitresse|Tu as attendu.
 maitresse|Puis tu as parlé.
@@ -1732,17 +1738,12 @@
 narrateur|La pomme de Nina est verte, un peu brillante.
 narrateur|Nina a envie de raconter son goûter.
 narrateur|Elle lève la main.
-narrateur|Il faut attendre.
+narrateur|Elle attend.
 narrateur|Quelqu'un parle.
-narrateur|Nina attend.
-narrateur|Elle pose la pomme devant elle.
 maitresse|Nina.
-enfant-f|J'ai une pomme.
+enfant-f|J'ai une pomme verte.
 maitresse|Merci.
-maitresse|Sur le tapis, puis au goûter, c'est pareil.
-maitresse|On lève la main.
-maitresse|On attend.
-maitresse|Puis on parle.</t>
+maitresse|Sur le tapis, puis au goûter, c'est pareil.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1774,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le soir, maman demande près de la porte. Alors, Nina ? J'ai levé la main. J'ai su attendre. Puis j'ai parlé. Bravo, Nina. Tu as fait du bon travail. Tu as attendu au goûter aussi ? Oui, maman. Nina met son manteau. Maman l'attend à la porte. Bravo. Tu as attendu. Puis tu as parlé.</t>
+          <t>Le soir, maman demande près de la porte. Alors, Nina ? J'ai montré la pomme de pin. J'ai attendu. Puis j'ai parlé. On la pose sur le rebord ? Oui, papa. La pomme de pin s'assoit près de la vitre. Tu as attendu au goûter aussi ? Oui, maman. Nina met son manteau. Le manteau sent encore la mousse.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1843,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1912,18 +1913,16 @@
         <is>
           <t>narrateur|Le soir, maman demande près de la porte.
 maman|Alors, Nina ?
-enfant-f|J'ai levé la main.
-enfant-f|J'ai su attendre.
+enfant-f|J'ai montré la pomme de pin.
+enfant-f|J'ai attendu.
 enfant-f|Puis j'ai parlé.
-papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
+papa|On la pose sur le rebord ?
+enfant-f|Oui, papa.
+narrateur|La pomme de pin s'assoit près de la vitre.
 maman|Tu as attendu au goûter aussi ?
 enfant-f|Oui, maman.
 narrateur|Nina met son manteau.
-narrateur|Maman l'attend à la porte.
-maman|Bravo.
-maman|Tu as attendu.
-maman|Puis tu as parlé.</t>
+narrateur|Le manteau sent encore la mousse.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1955,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Nina. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>La pomme de pin attend sur le rebord. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Nina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2095,15 +2094,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai levé la main.
+          <t>enfant-f|La pomme de pin attend sur le rebord.
+enfant-f|J'ai levé la main.
 enfant-f|J'ai attendu.
 enfant-f|Puis j'ai parlé.
 maman|Bravo, Nina.
-papa|Tu as fait du bon travail.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2193,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La pomme de pin attend sur le rebord. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Nina. L'histoire est finie.</t>
+          <t>La pomme de pin attend sur le rebord. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pomme de pin attend sur le rebord. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Nina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,8 +2098,7 @@
 enfant-f|J'ai levé la main.
 enfant-f|J'ai attendu.
 enfant-f|Puis j'ai parlé.
-maman|Bravo, Nina.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Nina.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2198,6 +2197,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>classe</t>
+          <t>entrée, classe, goûter, puis maison</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Idris, maman, maîtresse</t>
+          <t>Nina, papa, maman, maîtresse</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La pomme de pin de Nina</t>
+          <t>Le cacao de la fenêtre</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée, classe, goûter, puis maison</t>
+          <t>sentier de mousse, refuge de montagne, fenêtre de cacao</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nina, papa, maman, maîtresse</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une pomme de pin roule dans la poche. Nina veut la montrer près du hérisson. Elle attend, elle parle, puis au goûter elle attend encore pour sa pomme verte.</t>
+          <t>Nina veut montrer sa pomme de pin et boire le cacao du refuge. Elle parle trop tôt. La vapeur et les voix couvrent. Elle lève la main, on l'entend.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une pomme de pin roule dans la poche. Elle chatouille les doigts, tout sec. Un filet d'escargot brille sur le mur. L'air sent la mousse froide. Maman tient le cartable de Nina. Le cartable est un peu humide, dehors. Tu vas t'asseoir sur le tapis ? Oui, maman. Je veux montrer la pomme de pin. Près du hérisson. La pomme verte est pour le goûter. Tu attends ton tour, d'accord ? D'accord, papa. En ce moment, Nina entre dans la classe. Au revoir, Nina. Bonne journée. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, encore. La pomme de pin reste dans la poche. La maîtresse montre une affiche. C'est un hérisson. Les piquants sont dessinés au crayon brun. On écoute d'abord l'affiche. Qui veut parler du hérisson ? Nina a une idée. Les piquants ressemblent à la pomme de pin. Elle a envie de le dire. Je veux parler des piquants.</t>
+          <t>La mousse des sapins colle aux chaussures. L'air sent la résine froide. Une pomme de pin roule dans la poche. Elle chatouille les doigts, tout sec. Le refuge a une fenêtre allumée. Tu as vu la vapeur, Nina ? Ça sent le cacao. Je veux en boire. Et montrer ma pomme de pin. On va le dire, à la fenêtre. En ce moment, maman parle vers le bois. Sa voix se mêle à la vapeur. Nina a les mots tout prêts. Du cacao ! Et ma pomme de pin ! Les mots tombent dans la vapeur chaude. Personne ne se tourne. Deux tasses fument, trop loin. Maman. Maman parle encore, un gant sur le rebord. Nina ferme la bouche. Elle lève la main, tout droit. La pomme de pin est dans l'autre main. Sa main reste en l'air, près de la vitre. La vapeur s'écarte un peu. Maman se tourne. Tu voulais dire quelque chose ? Du cacao. Et ça, pour le rebord. Je t'entends, maintenant. Une tasse chaude arrive, toute ronde. Nina pose la pomme de pin sur le bois. Elle ressemble à un hérisson. Merci, Nina. Tu as attendu, et je t'ai entendue. Le cacao brûle un peu la lèvre. Il sent le bois et le lait. On souffle ensemble ? Fffff.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idris arrive en classe avec maman. Maman dit au revoir. Idris s'assoit sur le tapis. La maîtresse pose une question. Idris a une idée. Il lève la main. Il faut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Un camarade parle d'abord. Idris attend encore. Puis la maîtresse dit : Idris, c'est ton tour. Idris parle. Il dit : le hérisson a des piquants. La maîtresse sourit. Plus tard, c'est le goûter. Idris a envie de raconter son goûter. Il lève la main. Il faut attendre. Une camarade parle. Idris attend. Puis la maîtresse dit : Idris. Idris parle. Il dit : j'ai une pomme. Sur le tapis, puis au goûter, c'est pareil. On lève la main. Il faut attendre. Puis parler. Le soir, maman demande. Idris dit : j'ai levé la main. J'ai su attendre. Puis j'ai parlé. Maman dit merci. Idris range son cartable.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La mousse des sapins colle aux chaussures. L'air sent la résine froide. Une pomme de pin roule dans la poche. Elle chatouille les doigts, tout sec. Le refuge a une fenêtre allumée. Tu as vu la vapeur, Nina ? Ça sent le cacao. Je veux en boire. Et montrer ma pomme de pin. On va le dire, à la fenêtre. En ce moment, maman parle vers le bois. Sa voix se mêle à la vapeur. Nina a les mots tout prêts. Du cacao ! Et ma pomme de pin ! Les mots tombent dans la vapeur chaude. Personne ne se tourne. Deux tasses fument, trop loin. Maman. Maman parle encore, un gant sur le rebord. Nina ferme la bouche. Elle lève la main, tout droit. La pomme de pin est dans l'autre main. Sa main reste en l'air, près de la vitre. La vapeur s'écarte un peu. Maman se tourne. Tu voulais dire quelque chose ? Du cacao. Et ça, pour le rebord. Je t'entends, maintenant. Une tasse chaude arrive, toute ronde. Nina pose la pomme de pin sur le bois. Elle ressemble à un hérisson. Merci, Nina. Tu as attendu, et je t'ai entendue. Le cacao brûle un peu la lèvre. Il sent le bois et le lait. On souffle ensemble ? Fffff.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1329,35 +1329,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une pomme de pin roule dans la poche.
+          <t>narrateur|La mousse des sapins colle aux chaussures.
+narrateur|L'air sent la résine froide.
+narrateur|Une pomme de pin roule dans la poche.
 narrateur|Elle chatouille les doigts, tout sec.
-narrateur|Un filet d'escargot brille sur le mur.
-narrateur|L'air sent la mousse froide.
-narrateur|Maman tient le cartable de Nina.
-maman|Le cartable est un peu humide, dehors.
-maman|Tu vas t'asseoir sur le tapis ?
-enfant-f|Oui, maman.
-enfant-f|Je veux montrer la pomme de pin.
-enfant-f|Près du hérisson.
-papa|La pomme verte est pour le goûter.
-papa|Tu attends ton tour, d'accord ?
-enfant-f|D'accord, papa.
-narrateur|En ce moment, Nina entre dans la classe.
-maman|Au revoir, Nina.
-maman|Bonne journée.
-enfant-f|Au revoir, maman.
-narrateur|Nina s'assoit sur le tapis.
-narrateur|Le tapis est un peu froid, encore.
-narrateur|La pomme de pin reste dans la poche.
-narrateur|La maîtresse montre une affiche.
-narrateur|C'est un hérisson.
-narrateur|Les piquants sont dessinés au crayon brun.
-maitresse|On écoute d'abord l'affiche.
-maitresse|Qui veut parler du hérisson ?
-narrateur|Nina a une idée.
-narrateur|Les piquants ressemblent à la pomme de pin.
-narrateur|Elle a envie de le dire.
-enfant-f|Je veux parler des piquants.</t>
+narrateur|Le refuge a une fenêtre allumée.
+maman|Tu as vu la vapeur, Nina ?
+enfant-f|Ça sent le cacao.
+enfant-f|Je veux en boire.
+enfant-f|Et montrer ma pomme de pin.
+maman|On va le dire, à la fenêtre.
+narrateur|En ce moment, maman parle vers le bois.
+narrateur|Sa voix se mêle à la vapeur.
+narrateur|Nina a les mots tout prêts.
+enfant-f|Du cacao !
+enfant-f|Et ma pomme de pin !
+narrateur|Les mots tombent dans la vapeur chaude.
+narrateur|Personne ne se tourne.
+narrateur|Deux tasses fument, trop loin.
+enfant-f|Maman.
+narrateur|Maman parle encore, un gant sur le rebord.
+narrateur|Nina ferme la bouche.
+narrateur|Elle lève la main, tout droit.
+narrateur|La pomme de pin est dans l'autre main.
+narrateur|Sa main reste en l'air, près de la vitre.
+narrateur|La vapeur s'écarte un peu.
+narrateur|Maman se tourne.
+maman|Tu voulais dire quelque chose ?
+enfant-f|Du cacao.
+enfant-f|Et ça, pour le rebord.
+maman|Je t'entends, maintenant.
+narrateur|Une tasse chaude arrive, toute ronde.
+narrateur|Nina pose la pomme de pin sur le bois.
+enfant-f|Elle ressemble à un hérisson.
+maman|Merci, Nina.
+maman|Tu as attendu, et je t'ai entendue.
+narrateur|Le cacao brûle un peu la lèvre.
+narrateur|Il sent le bois et le lait.
+maman|On souffle ensemble ?
+enfant-f|Fffff.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1394,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idris veut parler. Que fait-il d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1424,7 +1434,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle lève la main et elle attend. Que fait Nina ?</t>
+          <t>Personne ne l'entend. Que fait Nina d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1466,14 +1476,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1573,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina lève la main. Sa main reste en l'air. Il faut attendre. Elle attend. Quelqu'un parle d'abord. Nina attend encore. Nina, c'est ton tour. Nina parle. Le hérisson a des piquants. Comme ma pomme de pin. Elle la pose près de l'affiche. Les piquants et les écailles se regardent. Merci, Nina. Tu as attendu. Puis tu as parlé. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme. La pomme de Nina est verte, un peu brillante. Nina a envie de raconter son goûter. Elle lève la main. Elle attend. Quelqu'un parle. Nina. J'ai une pomme verte. Merci. Sur le tapis, puis au goûter, c'est pareil.</t>
+          <t>La pomme de pin sèche sur le rebord. Nina souffle encore sur la tasse. Un nuage court sur le cacao. Il est moins chaud. Tu goûtes ? Oui. Une moustache brune reste au-dessus de la lèvre. Tu m'as entendue. Oui. Quand la vapeur s'est écartée. Quand ta main était là. Un grelot tinte, plus bas sur le sentier. La mousse brille encore aux chaussures. Ta pomme de pin tient bien ? Sur le bois, oui. Nina la tourne d'un doigt. Les écailles font un tout petit bruit. On la reprend, après ? Dans la poche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idris a levé la main. Il a attendu. &lt;emphasis level="moderate"&gt;puis&lt;/emphasis&gt; il a parlé. C'était son tour.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pomme de pin sèche sur le rebord. Nina souffle encore sur la tasse. Un nuage court sur le cacao. Il est moins chaud. Tu goûtes ? Oui. Une moustache brune reste au-dessus de la lèvre. Tu m'as entendue. Oui. Quand la vapeur s'est écartée. Quand ta main était là. Un grelot tinte, plus bas sur le sentier. La mousse brille encore aux chaussures. Ta pomme de pin tient bien ? Sur le bois, oui. Nina la tourne d'un doigt. Les écailles font un tout petit bruit. On la reprend, après ? Dans la poche.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1717,33 +1727,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina lève la main.
-narrateur|Sa main reste en l'air.
-narrateur|Il faut attendre.
-narrateur|Elle attend.
-narrateur|Quelqu'un parle d'abord.
-narrateur|Nina attend encore.
-maitresse|Nina, c'est ton tour.
-narrateur|Nina parle.
-enfant-f|Le hérisson a des piquants.
-enfant-f|Comme ma pomme de pin.
-narrateur|Elle la pose près de l'affiche.
-narrateur|Les piquants et les écailles se regardent.
-maitresse|Merci, Nina.
-maitresse|Tu as attendu.
-maitresse|Puis tu as parlé.
-narrateur|Plus tard, c'est le goûter.
-narrateur|Les boîtes s'ouvrent.
-narrateur|Ça sent la pomme.
-narrateur|La pomme de Nina est verte, un peu brillante.
-narrateur|Nina a envie de raconter son goûter.
-narrateur|Elle lève la main.
-narrateur|Elle attend.
-narrateur|Quelqu'un parle.
-maitresse|Nina.
-enfant-f|J'ai une pomme verte.
-maitresse|Merci.
-maitresse|Sur le tapis, puis au goûter, c'est pareil.</t>
+          <t>narrateur|La pomme de pin sèche sur le rebord.
+narrateur|Nina souffle encore sur la tasse.
+narrateur|Un nuage court sur le cacao.
+enfant-f|Il est moins chaud.
+maman|Tu goûtes ?
+enfant-f|Oui.
+narrateur|Une moustache brune reste au-dessus de la lèvre.
+enfant-f|Tu m'as entendue.
+maman|Oui.
+maman|Quand la vapeur s'est écartée.
+maman|Quand ta main était là.
+narrateur|Un grelot tinte, plus bas sur le sentier.
+narrateur|La mousse brille encore aux chaussures.
+maman|Ta pomme de pin tient bien ?
+enfant-f|Sur le bois, oui.
+narrateur|Nina la tourne d'un doigt.
+narrateur|Les écailles font un tout petit bruit.
+maman|On la reprend, après ?
+enfant-f|Dans la poche.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1775,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le soir, maman demande près de la porte. Alors, Nina ? J'ai montré la pomme de pin. J'ai attendu. Puis j'ai parlé. On la pose sur le rebord ? Oui, papa. La pomme de pin s'assoit près de la vitre. Tu as attendu au goûter aussi ? Oui, maman. Nina met son manteau. Le manteau sent encore la mousse.</t>
+          <t>La tasse est vide, encore chaude. Nina reprend la pomme de pin. On redescend ? Oui. J'ai bu le cacao. Oui. Je t'ai entendue. Le sentier sent la mousse et le lait. La fenêtre reste allumée, plus loin. Elle est bien dans la poche ? Elle chatouille encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idris met son manteau. Maman l'attend à la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tasse est vide, encore chaude. Nina reprend la pomme de pin. On redescend ? Oui. J'ai bu le cacao. Oui. Je t'ai entendue. Le sentier sent la mousse et le lait. La fenêtre reste allumée, plus loin. Elle est bien dans la poche ? Elle chatouille encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1911,18 +1913,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, maman demande près de la porte.
-maman|Alors, Nina ?
-enfant-f|J'ai montré la pomme de pin.
-enfant-f|J'ai attendu.
-enfant-f|Puis j'ai parlé.
-papa|On la pose sur le rebord ?
-enfant-f|Oui, papa.
-narrateur|La pomme de pin s'assoit près de la vitre.
-maman|Tu as attendu au goûter aussi ?
-enfant-f|Oui, maman.
-narrateur|Nina met son manteau.
-narrateur|Le manteau sent encore la mousse.</t>
+          <t>narrateur|La tasse est vide, encore chaude.
+narrateur|Nina reprend la pomme de pin.
+maman|On redescend ?
+enfant-f|Oui.
+enfant-f|J'ai bu le cacao.
+maman|Oui.
+maman|Je t'ai entendue.
+narrateur|Le sentier sent la mousse et le lait.
+narrateur|La fenêtre reste allumée, plus loin.
+maman|Elle est bien dans la poche ?
+enfant-f|Elle chatouille encore.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1954,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La pomme de pin attend sur le rebord. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Nina.</t>
+          <t>La pomme de pin chatouille la poche. Tu m'as entendue. Oui. Une moustache de cacao sèche un peu. Les sapins sentent encore la résine.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La pomme de pin attend sur le rebord. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Nina.</t>
+          <t>La pomme de pin chatouille la poche. Tu m'as entendue. Oui. Une moustache de cacao sèche un peu. Les sapins sentent encore la résine.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2022,7 +2023,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2094,11 +2095,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|La pomme de pin attend sur le rebord.
-enfant-f|J'ai levé la main.
-enfant-f|J'ai attendu.
-enfant-f|Puis j'ai parlé.
-maman|Bravo, Nina.</t>
+          <t>narrateur|La pomme de pin chatouille la poche.
+enfant-f|Tu m'as entendue.
+maman|Oui.
+narrateur|Une moustache de cacao sèche un peu.
+narrateur|Les sapins sentent encore la résine.</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2204,6 +2205,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.002-04.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le cacao de la fenêtre</t>
+          <t>La pomme de pin de Nina</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sentier de mousse, refuge de montagne, fenêtre de cacao</t>
+          <t>entrée, classe, goûter, puis maison</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nina, maman</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina veut montrer sa pomme de pin et boire le cacao du refuge. Elle parle trop tôt. La vapeur et les voix couvrent. Elle lève la main, on l'entend.</t>
+          <t>Un filet d'escargot brille sur le mur. Sur une écaille, un éclat de mousse brille. Nina veut montrer la pomme de pin, maintenant. Elle tire trop vite : les mots se perdent. À la classe, elle ouvre la bouche trop tôt. Elle refuse de foncer, lève la main, attend, parle. Merci vécu. L'éclat de mousse tient sur l'écaille.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La mousse des sapins colle aux chaussures. L'air sent la résine froide. Une pomme de pin roule dans la poche. Elle chatouille les doigts, tout sec. Le refuge a une fenêtre allumée. Tu as vu la vapeur, Nina ? Ça sent le cacao. Je veux en boire. Et montrer ma pomme de pin. On va le dire, à la fenêtre. En ce moment, maman parle vers le bois. Sa voix se mêle à la vapeur. Nina a les mots tout prêts. Du cacao ! Et ma pomme de pin ! Les mots tombent dans la vapeur chaude. Personne ne se tourne. Deux tasses fument, trop loin. Maman. Maman parle encore, un gant sur le rebord. Nina ferme la bouche. Elle lève la main, tout droit. La pomme de pin est dans l'autre main. Sa main reste en l'air, près de la vitre. La vapeur s'écarte un peu. Maman se tourne. Tu voulais dire quelque chose ? Du cacao. Et ça, pour le rebord. Je t'entends, maintenant. Une tasse chaude arrive, toute ronde. Nina pose la pomme de pin sur le bois. Elle ressemble à un hérisson. Merci, Nina. Tu as attendu, et je t'ai entendue. Le cacao brûle un peu la lèvre. Il sent le bois et le lait. On souffle ensemble ? Fffff.</t>
+          <t>Un filet d'escargot brille sur le mur. Il est argenté, un peu visqueux. L'air sent la mousse froide. Nina connaît ce mur de l'entrée. Ce filet, lui, est nouveau. Une pomme de pin roule dans la poche. Elle chatouille les doigts, sèche. Sur une écaille, un éclat de mousse brille. Il est vert, maman. C'est la mousse du sentier. Le cartable est un peu humide, dehors. Maman tient le cartable de Nina. Le tissu sent la pluie et le bois. Je veux montrer la pomme de pin, maintenant ! Près du hérisson. La pomme verte est pour le goûter. Papa parle près du cartable, une main sur le tissu. Je la sors ! Nina tire trop vite. La pomme de pin glisse, presque. Les mots se cognent à ceux de papa. Personne ne tourne la tête. Oh. L'éclat de mousse tremble, puis tient. Le sourire de Nina disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Ça ne veut pas. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu veux la montrer ? Oui, papa. Tu vas t'asseoir sur le tapis ? D'accord, maman. En ce moment, Nina entre dans la classe. Au revoir, Nina. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, sous les genoux. La pomme de pin reste dans la poche. Près du tableau, la maîtresse montre une affiche. C'est un hérisson. Les piquants sont dessinés au crayon brun. La classe écoute l'affiche. Nina a une idée. Les piquants ressemblent à la pomme de pin. Je veux parler des piquants.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La mousse des sapins colle aux chaussures. L'air sent la résine froide. Une pomme de pin roule dans la poche. Elle chatouille les doigts, tout sec. Le refuge a une fenêtre allumée. Tu as vu la vapeur, Nina ? Ça sent le cacao. Je veux en boire. Et montrer ma pomme de pin. On va le dire, à la fenêtre. En ce moment, maman parle vers le bois. Sa voix se mêle à la vapeur. Nina a les mots tout prêts. Du cacao ! Et ma pomme de pin ! Les mots tombent dans la vapeur chaude. Personne ne se tourne. Deux tasses fument, trop loin. Maman. Maman parle encore, un gant sur le rebord. Nina ferme la bouche. Elle lève la main, tout droit. La pomme de pin est dans l'autre main. Sa main reste en l'air, près de la vitre. La vapeur s'écarte un peu. Maman se tourne. Tu voulais dire quelque chose ? Du cacao. Et ça, pour le rebord. Je t'entends, maintenant. Une tasse chaude arrive, toute ronde. Nina pose la pomme de pin sur le bois. Elle ressemble à un hérisson. Merci, Nina. Tu as attendu, et je t'ai entendue. Le cacao brûle un peu la lèvre. Il sent le bois et le lait. On souffle ensemble ? Fffff.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un filet d'escargot brille sur le mur. Il est argenté, un peu visqueux. L'air sent la mousse froide. Nina connaît ce mur de l'entrée. Ce filet, lui, est nouveau. Une pomme de pin roule dans la poche. Elle chatouille les doigts, sèche. Sur une écaille, un &lt;emphasis level="moderate"&gt;éclat de mousse&lt;/emphasis&gt; brille. Il est vert, maman. C'est la mousse du sentier. Le cartable est un peu humide, dehors. Maman tient le cartable de Nina. Le tissu sent la pluie et le bois. Je veux montrer la pomme de pin, maintenant ! Près du hérisson. La pomme verte est pour le goûter. Papa parle près du cartable, une main sur le tissu. Je la sors ! Nina tire trop vite. La pomme de pin glisse, presque. Les mots se cognent à ceux de papa. Personne ne tourne la tête. Oh. L'éclat de mousse tremble, puis tient. Le sourire de Nina disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Ça ne veut pas. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu veux la montrer ? Oui, papa. Tu vas t'asseoir sur le tapis ? D'accord, maman. En ce moment, Nina entre dans la classe. Au revoir, Nina. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, sous les genoux. La pomme de pin reste dans la poche. Près du tableau, la maîtresse montre une affiche. C'est un hérisson. Les piquants sont dessinés au crayon brun. La classe écoute l'affiche. Nina a une idée. Les piquants ressemblent à la pomme de pin. Je veux parler des piquants.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Idris arrive en classe avec maman. Maman dit au revoir. Idris s'assoit sur le tapis. La maîtresse pose une question. Idris a une idée. Il lève la main. Il faut &lt;emphasis&gt;attendre&lt;/emphasis&gt;. Un camarade parle d'abord. Idris attend encore. Puis la maîtresse dit : Idris, c'est ton tour. Idris parle. Il dit : le hérisson a des piquants. La maîtresse sourit. Plus tard, c'est le goûter. Idris a envie de raconter son goûter. Il lève la main. Il faut attendre. Une camarade parle. Idris attend. Puis la maîtresse dit : Idris. Idris parle. Il dit : j'ai une pomme. Sur le tapis, puis au goûter, c'est pareil. On lève la main. Il faut attendre. Puis parler. Le soir, maman demande. Idris dit : j'ai levé la main. J'ai su attendre. Puis j'ai parlé. Maman dit merci. Idris range son cartable. [pause]</t>
+          <t>Un filet d'escargot brille sur le mur. Il est argenté, un peu visqueux. L'air sent la mousse froide. Nina connaît ce mur de l'entrée. Ce filet, lui, est nouveau. Une pomme de pin roule dans la poche. Elle chatouille les doigts, sèche. Sur une écaille, un &lt;emphasis&gt;éclat de mousse&lt;/emphasis&gt; brille. Il est vert, maman. C'est la mousse du sentier. Le cartable est un peu humide, dehors. Maman tient le cartable de Nina. Le tissu sent la pluie et le bois. Je veux montrer la pomme de pin, maintenant ! Près du hérisson. La pomme verte est pour le goûter. Papa parle près du cartable, une main sur le tissu. Je la sors ! Nina tire trop vite. La pomme de pin glisse, presque. Les mots se cognent à ceux de papa. Personne ne tourne la tête. Oh. L'éclat de mousse tremble, puis tient. Le sourire de Nina disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Ça ne veut pas. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu veux la montrer ? Oui, papa. Tu vas t'asseoir sur le tapis ? D'accord, maman. En ce moment, Nina entre dans la classe. Au revoir, Nina. Au revoir, maman. Nina s'assoit sur le tapis. Le tapis est un peu froid, sous les genoux. La pomme de pin reste dans la poche. Près du tableau, la maîtresse montre une affiche. C'est un hérisson. Les piquants sont dessinés au crayon brun. La classe écoute l'affiche. Nina a une idée. Les piquants ressemblent à la pomme de pin. Je veux parler des piquants. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>attendre</t>
+          <t>éclat de mousse</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,48 +1326,59 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_montrer_la_pomme_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La mousse des sapins colle aux chaussures.
-narrateur|L'air sent la résine froide.
+          <t>narrateur|Un filet d'escargot brille sur le mur.
+narrateur|Il est argenté, un peu visqueux.
+narrateur|L'air sent la mousse froide.
+narrateur|Nina connaît ce mur de l'entrée.
+narrateur|Ce filet, lui, est nouveau.
 narrateur|Une pomme de pin roule dans la poche.
-narrateur|Elle chatouille les doigts, tout sec.
-narrateur|Le refuge a une fenêtre allumée.
-maman|Tu as vu la vapeur, Nina ?
-enfant-f|Ça sent le cacao.
-enfant-f|Je veux en boire.
-enfant-f|Et montrer ma pomme de pin.
-maman|On va le dire, à la fenêtre.
-narrateur|En ce moment, maman parle vers le bois.
-narrateur|Sa voix se mêle à la vapeur.
-narrateur|Nina a les mots tout prêts.
-enfant-f|Du cacao !
-enfant-f|Et ma pomme de pin !
-narrateur|Les mots tombent dans la vapeur chaude.
-narrateur|Personne ne se tourne.
-narrateur|Deux tasses fument, trop loin.
-enfant-f|Maman.
-narrateur|Maman parle encore, un gant sur le rebord.
-narrateur|Nina ferme la bouche.
-narrateur|Elle lève la main, tout droit.
-narrateur|La pomme de pin est dans l'autre main.
-narrateur|Sa main reste en l'air, près de la vitre.
-narrateur|La vapeur s'écarte un peu.
-narrateur|Maman se tourne.
-maman|Tu voulais dire quelque chose ?
-enfant-f|Du cacao.
-enfant-f|Et ça, pour le rebord.
-maman|Je t'entends, maintenant.
-narrateur|Une tasse chaude arrive, toute ronde.
-narrateur|Nina pose la pomme de pin sur le bois.
-enfant-f|Elle ressemble à un hérisson.
-maman|Merci, Nina.
-maman|Tu as attendu, et je t'ai entendue.
-narrateur|Le cacao brûle un peu la lèvre.
-narrateur|Il sent le bois et le lait.
-maman|On souffle ensemble ?
-enfant-f|Fffff.</t>
+narrateur|Elle chatouille les doigts, sèche.
+narrateur|Sur une écaille, un éclat de mousse brille.
+enfant-f|Il est vert, maman.
+maman|C'est la mousse du sentier.
+papa|Le cartable est un peu humide, dehors.
+narrateur|Maman tient le cartable de Nina.
+narrateur|Le tissu sent la pluie et le bois.
+enfant-f|Je veux montrer la pomme de pin, maintenant !
+enfant-f|Près du hérisson.
+papa|La pomme verte est pour le goûter.
+narrateur|Papa parle près du cartable, une main sur le tissu.
+enfant-f|Je la sors !
+narrateur|Nina tire trop vite.
+narrateur|La pomme de pin glisse, presque.
+narrateur|Les mots se cognent à ceux de papa.
+narrateur|Personne ne tourne la tête.
+enfant-f|Oh.
+narrateur|L'éclat de mousse tremble, puis tient.
+narrateur|Le sourire de Nina disparaît.
+narrateur|Dans sa poitrine, envie et inquiétude se bousculent.
+enfant-f|Ça ne veut pas.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa se baisse à sa hauteur.
+papa|Tu veux la montrer ?
+enfant-f|Oui, papa.
+maman|Tu vas t'asseoir sur le tapis ?
+enfant-f|D'accord, maman.
+narrateur|En ce moment, Nina entre dans la classe.
+maman|Au revoir, Nina.
+enfant-f|Au revoir, maman.
+narrateur|Nina s'assoit sur le tapis.
+narrateur|Le tapis est un peu froid, sous les genoux.
+narrateur|La pomme de pin reste dans la poche.
+narrateur|Près du tableau, la maîtresse montre une affiche.
+narrateur|C'est un hérisson.
+narrateur|Les piquants sont dessinés au crayon brun.
+narrateur|La classe écoute l'affiche.
+narrateur|Nina a une idée.
+narrateur|Les piquants ressemblent à la pomme de pin.
+enfant-f|Je veux parler des piquants.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1404,12 +1415,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nina veut parler. Que fait-elle d'abord ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina veut &lt;emphasis level="moderate"&gt;parler&lt;/emphasis&gt;. Que fait-elle d'abord ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Idris veut parler. Que fait-il d'abord ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nina veut &lt;emphasis&gt;parler&lt;/emphasis&gt;. Que fait-elle d'abord ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1434,7 +1445,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Personne ne l'entend. Que fait Nina d'abord ?</t>
+          <t>Elle lève la main et elle attend. Que fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1472,7 +1483,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1480,10 +1491,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1498,34 +1509,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>parler</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1534,23 +1549,23 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=elle_attend_puis_parle; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1583,17 +1598,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>La pomme de pin sèche sur le rebord. Nina souffle encore sur la tasse. Un nuage court sur le cacao. Il est moins chaud. Tu goûtes ? Oui. Une moustache brune reste au-dessus de la lèvre. Tu m'as entendue. Oui. Quand la vapeur s'est écartée. Quand ta main était là. Un grelot tinte, plus bas sur le sentier. La mousse brille encore aux chaussures. Ta pomme de pin tient bien ? Sur le bois, oui. Nina la tourne d'un doigt. Les écailles font un tout petit bruit. On la reprend, après ? Dans la poche.</t>
+          <t>Nina ouvre la bouche trop vite. Les piquants, comme ma pomme de pin ! Un camarade parle, près de l'affiche. Le hérisson a des piquants. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Nina refuse de foncer. Elle referme la bouche. Elle lève la main, près du tapis. Sa main reste en l'air. Le camarade finit sa phrase. Nina attend que le silence arrive. Sur l'écaille, l'éclat de mousse brille. Je peux dire quelque chose ? La classe tourne un peu la tête. Le hérisson a des piquants. Comme ma pomme de pin. Elle la pose près de l'affiche. Les piquants et les écailles se regardent. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme verte. Nina a envie de raconter son goûter. J'ai une pomme ! Les voix se mélangent, près des boîtes. Nina referme la bouche. Elle lève la main. Elle attend. Une boîte se ferme, un peu plus loin. J'ai une pomme verte. Le soir, la porte s'ouvre. Te voilà, Nina. Le manteau sent la mousse. Nina pose le cartable contre le mur. J'ai montré la pomme de pin. Les piquants, comme les écailles. Merci, Nina. Papa a entendu toute la phrase. Tu veux ta pomme ? Oui, maman. Le ventre de Nina se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>La pomme de pin sèche sur le rebord. Nina souffle encore sur la tasse. Un nuage court sur le cacao. Il est moins chaud. Tu goûtes ? Oui. Une moustache brune reste au-dessus de la lèvre. Tu m'as entendue. Oui. Quand la vapeur s'est écartée. Quand ta main était là. Un grelot tinte, plus bas sur le sentier. La mousse brille encore aux chaussures. Ta pomme de pin tient bien ? Sur le bois, oui. Nina la tourne d'un doigt. Les écailles font un tout petit bruit. On la reprend, après ? Dans la poche.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina ouvre la bouche trop vite. Les piquants, comme ma pomme de pin ! Un camarade parle, près de l'affiche. Le hérisson a des piquants. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Nina refuse de foncer. Elle referme la bouche. Elle lève la main, près du tapis. Sa main reste en l'air. Le camarade finit sa phrase. Nina attend que le &lt;emphasis level="moderate"&gt;silence&lt;/emphasis&gt; arrive. Sur l'écaille, l'éclat de mousse brille. Je peux dire quelque chose ? La classe tourne un peu la tête. Le hérisson a des piquants. Comme ma pomme de pin. Elle la pose près de l'affiche. Les piquants et les écailles se regardent. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme verte. Nina a envie de raconter son goûter. J'ai une pomme ! Les voix se mélangent, près des boîtes. Nina referme la bouche. Elle lève la main. Elle attend. Une boîte se ferme, un peu plus loin. J'ai une pomme verte. Le soir, la porte s'ouvre. Te voilà, Nina. Le manteau sent la mousse. Nina pose le cartable contre le mur. J'ai montré la pomme de pin. Les piquants, comme les écailles. Merci, Nina. Papa a entendu toute la phrase. Tu veux ta pomme ? Oui, maman. Le ventre de Nina se desserre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Idris a levé la main. Il a attendu. &lt;emphasis&gt;puis&lt;/emphasis&gt; il a parlé. C'était son tour. [pause]</t>
+          <t>Nina ouvre la bouche trop vite. Les piquants, comme ma pomme de pin ! Un camarade parle, près de l'affiche. Le hérisson a des piquants. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Nina refuse de foncer. Elle referme la bouche. Elle lève la main, près du tapis. Sa main reste en l'air. Le camarade finit sa phrase. Nina attend que le &lt;emphasis&gt;silence&lt;/emphasis&gt; arrive. Sur l'écaille, l'éclat de mousse brille. Je peux dire quelque chose ? La classe tourne un peu la tête. Le hérisson a des piquants. Comme ma pomme de pin. Elle la pose près de l'affiche. Les piquants et les écailles se regardent. Plus tard, c'est le goûter. Les boîtes s'ouvrent. Ça sent la pomme verte. Nina a envie de raconter son goûter. J'ai une pomme ! Les voix se mélangent, près des boîtes. Nina referme la bouche. Elle lève la main. Elle attend. Une boîte se ferme, un peu plus loin. J'ai une pomme verte. Le soir, la porte s'ouvre. Te voilà, Nina. Le manteau sent la mousse. Nina pose le cartable contre le mur. J'ai montré la pomme de pin. Les piquants, comme les écailles. Merci, Nina. Papa a entendu toute la phrase. Tu veux ta pomme ? Oui, maman. Le ventre de Nina se desserre. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1640,7 +1655,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,30 +1689,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>puis</t>
+          <t>silence</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1706,10 +1721,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1722,30 +1737,53 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_attend_puis_on_l_entend; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|La pomme de pin sèche sur le rebord.
-narrateur|Nina souffle encore sur la tasse.
-narrateur|Un nuage court sur le cacao.
-enfant-f|Il est moins chaud.
-maman|Tu goûtes ?
-enfant-f|Oui.
-narrateur|Une moustache brune reste au-dessus de la lèvre.
-enfant-f|Tu m'as entendue.
-maman|Oui.
-maman|Quand la vapeur s'est écartée.
-maman|Quand ta main était là.
-narrateur|Un grelot tinte, plus bas sur le sentier.
-narrateur|La mousse brille encore aux chaussures.
-maman|Ta pomme de pin tient bien ?
-enfant-f|Sur le bois, oui.
-narrateur|Nina la tourne d'un doigt.
-narrateur|Les écailles font un tout petit bruit.
-maman|On la reprend, après ?
-enfant-f|Dans la poche.</t>
+          <t>narrateur|Nina ouvre la bouche trop vite.
+enfant-f|Les piquants, comme ma pomme de pin !
+narrateur|Un camarade parle, près de l'affiche.
+copain|Le hérisson a des piquants.
+narrateur|Les deux voix se mélangent.
+enfant-f|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Nina refuse de foncer.
+narrateur|Elle referme la bouche.
+narrateur|Elle lève la main, près du tapis.
+narrateur|Sa main reste en l'air.
+narrateur|Le camarade finit sa phrase.
+narrateur|Nina attend que le silence arrive.
+narrateur|Sur l'écaille, l'éclat de mousse brille.
+enfant-f|Je peux dire quelque chose ?
+narrateur|La classe tourne un peu la tête.
+enfant-f|Le hérisson a des piquants.
+enfant-f|Comme ma pomme de pin.
+narrateur|Elle la pose près de l'affiche.
+narrateur|Les piquants et les écailles se regardent.
+narrateur|Plus tard, c'est le goûter.
+narrateur|Les boîtes s'ouvrent.
+narrateur|Ça sent la pomme verte.
+narrateur|Nina a envie de raconter son goûter.
+enfant-f|J'ai une pomme !
+narrateur|Les voix se mélangent, près des boîtes.
+narrateur|Nina referme la bouche.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+narrateur|Une boîte se ferme, un peu plus loin.
+enfant-f|J'ai une pomme verte.
+narrateur|Le soir, la porte s'ouvre.
+maman|Te voilà, Nina.
+papa|Le manteau sent la mousse.
+narrateur|Nina pose le cartable contre le mur.
+enfant-f|J'ai montré la pomme de pin.
+enfant-f|Les piquants, comme les écailles.
+papa|Merci, Nina.
+narrateur|Papa a entendu toute la phrase.
+maman|Tu veux ta pomme ?
+enfant-f|Oui, maman.
+narrateur|Le ventre de Nina se desserre.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1777,17 +1815,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La tasse est vide, encore chaude. Nina reprend la pomme de pin. On redescend ? Oui. J'ai bu le cacao. Oui. Je t'ai entendue. Le sentier sent la mousse et le lait. La fenêtre reste allumée, plus loin. Elle est bien dans la poche ? Elle chatouille encore.</t>
+          <t>Nina veut tout dire, d'un coup. Elle prend la pomme et la pomme de pin. La pomme verte glisse vers le sol. La pomme de pin roule vers le rebord. Ça tombe ! Nina veut foncer, d'un coup. Nina refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde la pomme de pin. Elle écoute l'entrée, un instant. Le filet d'escargot sèche un peu, sur le mur. Sur le rebord, l'éclat de mousse brille. Comme ce matin ! Tu le vois, toi ? Oui, sur cette écaille. Nina pose la pomme de pin, d'abord. Puis elle rattrape la pomme verte. La pomme, Nina ? Oui. Elle s'assoit. La pomme est lisse, un peu froide. Elle croque. Le jus est doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>La tasse est vide, encore chaude. Nina reprend la pomme de pin. On redescend ? Oui. J'ai bu le cacao. Oui. Je t'ai entendue. Le sentier sent la mousse et le lait. La fenêtre reste allumée, plus loin. Elle est bien dans la poche ? Elle chatouille encore.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina veut tout dire, d'un coup. Elle prend la pomme et la pomme de pin. La pomme verte glisse vers le sol. La pomme de pin roule vers le rebord. Ça tombe ! Nina veut foncer, d'un coup. Nina refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde la pomme de pin. Elle écoute l'entrée, un instant. Le filet d'escargot sèche un peu, sur le mur. Sur le rebord, l'&lt;emphasis level="moderate"&gt;éclat de mousse&lt;/emphasis&gt; brille. Comme ce matin ! Tu le vois, toi ? Oui, sur cette écaille. Nina pose la pomme de pin, d'abord. Puis elle rattrape la pomme verte. La pomme, Nina ? Oui. Elle s'assoit. La pomme est lisse, un peu froide. Elle croque. Le jus est doux.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Idris met son manteau. Maman l'attend à la porte. [pause]</t>
+          <t>&lt;low-pitch&gt;Nina veut tout dire, d'un coup. Elle prend la pomme et la pomme de pin. La pomme verte glisse vers le sol. La pomme de pin roule vers le rebord. Ça tombe ! Nina veut foncer, d'un coup. Nina refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde la pomme de pin. Elle écoute l'entrée, un instant. Le filet d'escargot sèche un peu, sur le mur. Sur le rebord, l'&lt;emphasis&gt;éclat de mousse&lt;/emphasis&gt; brille. Comme ce matin ! Tu le vois, toi ? Oui, sur cette écaille. Nina pose la pomme de pin, d'abord. Puis elle rattrape la pomme verte. La pomme, Nina ? Oui. Elle s'assoit. La pomme est lisse, un peu froide. Elle croque. Le jus est doux.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1834,7 +1872,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1842,22 +1880,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1866,28 +1908,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de mousse</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1896,39 +1942,57 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_retrouve_l_eclat; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La tasse est vide, encore chaude.
-narrateur|Nina reprend la pomme de pin.
-maman|On redescend ?
+          <t>narrateur|Nina veut tout dire, d'un coup.
+narrateur|Elle prend la pomme et la pomme de pin.
+narrateur|La pomme verte glisse vers le sol.
+narrateur|La pomme de pin roule vers le rebord.
+enfant-f|Ça tombe !
+narrateur|Nina veut foncer, d'un coup.
+narrateur|Nina refuse de foncer.
+narrateur|Ses épaules se serrent un peu.
+narrateur|Ça tape, dans sa poitrine.
+narrateur|Personne ne dit la suite.
+narrateur|Elle regarde la pomme de pin.
+narrateur|Elle écoute l'entrée, un instant.
+narrateur|Le filet d'escargot sèche un peu, sur le mur.
+narrateur|Sur le rebord, l'éclat de mousse brille.
+enfant-f|Comme ce matin !
+papa|Tu le vois, toi ?
+enfant-f|Oui, sur cette écaille.
+narrateur|Nina pose la pomme de pin, d'abord.
+narrateur|Puis elle rattrape la pomme verte.
+maman|La pomme, Nina ?
 enfant-f|Oui.
-enfant-f|J'ai bu le cacao.
-maman|Oui.
-maman|Je t'ai entendue.
-narrateur|Le sentier sent la mousse et le lait.
-narrateur|La fenêtre reste allumée, plus loin.
-maman|Elle est bien dans la poche ?
-enfant-f|Elle chatouille encore.</t>
+narrateur|Elle s'assoit.
+narrateur|La pomme est lisse, un peu froide.
+narrateur|Elle croque.
+narrateur|Le jus est doux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>porte,manteau</t>
+          <t>pomme,rebord</t>
         </is>
       </c>
     </row>
@@ -1955,17 +2019,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La pomme de pin chatouille la poche. Tu m'as entendue. Oui. Une moustache de cacao sèche un peu. Les sapins sentent encore la résine.</t>
+          <t>La pomme de pin attend sur le rebord. Le filet d'escargot sèche sur le mur. L'éclat est là, papa. Tu le vois sur l'écaille ? Oui, papa. On est bien, ici. La pomme verte repose près de la fenêtre. La fenêtre tremble moins. On m'a entendue. On t'a entendue, Nina. Oui, maman. Nina pose la joue près des écailles. Les écailles sont sèches, un peu rudes. C'est froid. Dehors, la mousse reste sur le sentier. L'éclat de mousse tient sur l'écaille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La pomme de pin chatouille la poche. Tu m'as entendue. Oui. Une moustache de cacao sèche un peu. Les sapins sentent encore la résine.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La pomme de pin attend sur le rebord. Le filet d'escargot sèche sur le mur. L'éclat est là, papa. Tu le vois sur l'écaille ? Oui, papa. On est bien, ici. La pomme verte repose près de la fenêtre. La fenêtre tremble moins. On m'a entendue. On t'a entendue, Nina. Oui, maman. Nina pose la joue près des écailles. Les écailles sont sèches, un peu rudes. C'est froid. Dehors, la mousse reste sur le sentier. L'&lt;emphasis level="moderate"&gt;éclat de mousse&lt;/emphasis&gt; tient sur l'écaille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La pomme de pin attend sur le rebord. Le filet d'escargot sèche sur le mur. L'éclat est là, papa. Tu le vois sur l'écaille ? Oui, papa. On est bien, ici. La pomme verte repose près de la fenêtre. La fenêtre tremble moins. On m'a entendue. On t'a entendue, Nina. Oui, maman. Nina pose la joue près des écailles. Les écailles sont sèches, un peu rudes. C'est froid. Dehors, la mousse reste sur le sentier. L'&lt;emphasis&gt;éclat de mousse&lt;/emphasis&gt; tient sur l'écaille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2012,18 +2076,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2032,12 +2096,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2046,17 +2110,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de mousse</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2065,11 +2133,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2078,28 +2146,48 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_l_ecaille; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|La pomme de pin chatouille la poche.
-enfant-f|Tu m'as entendue.
-maman|Oui.
-narrateur|Une moustache de cacao sèche un peu.
-narrateur|Les sapins sentent encore la résine.</t>
+          <t>narrateur|La pomme de pin attend sur le rebord.
+narrateur|Le filet d'escargot sèche sur le mur.
+enfant-f|L'éclat est là, papa.
+papa|Tu le vois sur l'écaille ?
+enfant-f|Oui, papa.
+maman|On est bien, ici.
+narrateur|La pomme verte repose près de la fenêtre.
+narrateur|La fenêtre tremble moins.
+enfant-f|On m'a entendue.
+maman|On t'a entendue, Nina.
+enfant-f|Oui, maman.
+narrateur|Nina pose la joue près des écailles.
+narrateur|Les écailles sont sèches, un peu rudes.
+enfant-f|C'est froid.
+narrateur|Dehors, la mousse reste sur le sentier.
+narrateur|L'éclat de mousse tient sur l'écaille.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>rebord,mousse</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2212,6 +2300,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
